--- a/src/staticfiles/study/templates/event_attestation_policies_import_template.xlsx
+++ b/src/staticfiles/study/templates/event_attestation_policies_import_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Attestation Policies" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Notes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Attestation Policies" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -717,7 +717,7 @@
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>I certify that the data entered in this eCRF are complete, accurate, and ae supported by the source documents</t>
+          <t>I certify that the data entered in this eCRF are complete, accurate, and are supported by the source documents</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>I certify that the data entered in this eCRF are complete, accurate, and ae supported by the source documents</t>
+          <t>I certify that the data entered in this eCRF are complete, accurate, and are supported by the source documents</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>I certify that the data entered in this eCRF are complete, accurate, and ae supported by the source documents</t>
+          <t>I certify that the data entered in this eCRF are complete, accurate, and are supported by the source documents</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>I certify that the data entered in this eCRF are complete, accurate, and ae supported by the source documents</t>
+          <t>I certify that the data entered in this eCRF are complete, accurate, and are supported by the source documents</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>I certify that the data entered in this eCRF are complete, accurate, and ae supported by the source documents</t>
+          <t>I certify that the data entered in this eCRF are complete, accurate, and are supported by the source documents</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>I certify that the data entered in this eCRF are complete, accurate, and ae supported by the source documents</t>
+          <t>I certify that the data entered in this eCRF are complete, accurate, and are supported by the source documents</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>I certify that the data entered in this eCRF are complete, accurate, and ae supported by the source documents</t>
+          <t>I certify that the data entered in this eCRF are complete, accurate, and are supported by the source documents</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>I certify that the data entered in this eCRF are complete, accurate, and ae supported by the source documents</t>
+          <t>I certify that the data entered in this eCRF are complete, accurate, and are supported by the source documents</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>I certify that the data entered in this eCRF are complete, accurate, and ae supported by the source documents</t>
+          <t>I certify that the data entered in this eCRF are complete, accurate, and are supported by the source documents</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>I certify that the data entered in this eCRF are complete, accurate, and ae supported by the source documents</t>
+          <t>I certify that the data entered in this eCRF are complete, accurate, and are supported by the source documents</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>I certify that the data entered in this eCRF are complete, accurate, and ae supported by the source documents</t>
+          <t>I certify that the data entered in this eCRF are complete, accurate, and are supported by the source documents</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>I certify that the data entered in this eCRF are complete, accurate, and ae supported by the source documents</t>
+          <t>I certify that the data entered in this eCRF are complete, accurate, and are supported by the source documents</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>I certify that the data entered in this eCRF are complete, accurate, and ae supported by the source documents</t>
+          <t>I certify that the data entered in this eCRF are complete, accurate, and are supported by the source documents</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>I certify that the data entered in this eCRF are complete, accurate, and ae supported by the source documents</t>
+          <t>I certify that the data entered in this eCRF are complete, accurate, and are supported by the source documents</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>I certify that the data entered in this eCRF are complete, accurate, and ae supported by the source documents</t>
+          <t>I certify that the data entered in this eCRF are complete, accurate, and are supported by the source documents</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>I certify that the data entered in this eCRF are complete, accurate, and ae supported by the source documents</t>
+          <t>I certify that the data entered in this eCRF are complete, accurate, and are supported by the source documents</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>I certify that the data entered in this eCRF are complete, accurate, and ae supported by the source documents</t>
+          <t>I certify that the data entered in this eCRF are complete, accurate, and are supported by the source documents</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>I certify that the data entered in this eCRF are complete, accurate, and ae supported by the source documents</t>
+          <t>I certify that the data entered in this eCRF are complete, accurate, and are supported by the source documents</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>I certify that the data entered in this eCRF are complete, accurate, and ae supported by the source documents</t>
+          <t>I certify that the data entered in this eCRF are complete, accurate, and are supported by the source documents</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>I certify that the data entered in this eCRF are complete, accurate, and ae supported by the source documents</t>
+          <t>I certify that the data entered in this eCRF are complete, accurate, and are supported by the source documents</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>I certify that the data entered in this eCRF are complete, accurate, and ae supported by the source documents</t>
+          <t>I certify that the data entered in this eCRF are complete, accurate, and are supported by the source documents</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>I certify that the data entered in this eCRF are complete, accurate, and ae supported by the source documents</t>
+          <t>I certify that the data entered in this eCRF are complete, accurate, and are supported by the source documents</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>I certify that the data entered in this eCRF are complete, accurate, and ae supported by the source documents</t>
+          <t>I certify that the data entered in this eCRF are complete, accurate, and are supported by the source documents</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>I certify that the data entered in this eCRF are complete, accurate, and ae supported by the source documents</t>
+          <t>I certify that the data entered in this eCRF are complete, accurate, and are supported by the source documents</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>I certify that the data entered in this eCRF are complete, accurate, and ae supported by the source documents</t>
+          <t>I certify that the data entered in this eCRF are complete, accurate, and are supported by the source documents</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2338,7 +2338,7 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>I certify that the data entered in this eCRF are complete, accurate, and ae supported by the source documents</t>
+          <t>I certify that the data entered in this eCRF are complete, accurate, and are supported by the source documents</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>I certify that the data entered in this eCRF are complete, accurate, and ae supported by the source documents</t>
+          <t>I certify that the data entered in this eCRF are complete, accurate, and are supported by the source documents</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>I certify that the data entered in this eCRF are complete, accurate, and ae supported by the source documents</t>
+          <t>I certify that the data entered in this eCRF are complete, accurate, and are supported by the source documents</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>I certify that the data entered in this eCRF are complete, accurate, and ae supported by the source documents</t>
+          <t>I certify that the data entered in this eCRF are complete, accurate, and are supported by the source documents</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>I certify that the data entered in this eCRF are complete, accurate, and ae supported by the source documents</t>
+          <t>I certify that the data entered in this eCRF are complete, accurate, and are supported by the source documents</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>I certify that the data entered in this eCRF are complete, accurate, and ae supported by the source documents</t>
+          <t>I certify that the data entered in this eCRF are complete, accurate, and are supported by the source documents</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>I certify that the data entered in this eCRF are complete, accurate, and ae supported by the source documents</t>
+          <t>I certify that the data entered in this eCRF are complete, accurate, and are supported by the source documents</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>I certify that the data entered in this eCRF are complete, accurate, and ae supported by the source documents</t>
+          <t>I certify that the data entered in this eCRF are complete, accurate, and are supported by the source documents</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>I certify that the data entered in this eCRF are complete, accurate, and ae supported by the source documents</t>
+          <t>I certify that the data entered in this eCRF are complete, accurate, and are supported by the source documents</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>I certify that the data entered in this eCRF are complete, accurate, and ae supported by the source documents</t>
+          <t>I certify that the data entered in this eCRF are complete, accurate, and are supported by the source documents</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>I certify that the data entered in this eCRF are complete, accurate, and ae supported by the source documents</t>
+          <t>I certify that the data entered in this eCRF are complete, accurate, and are supported by the source documents</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>I certify that the data entered in this eCRF are complete, accurate, and ae supported by the source documents</t>
+          <t>I certify that the data entered in this eCRF are complete, accurate, and are supported by the source documents</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>I certify that the data entered in this eCRF are complete, accurate, and ae supported by the source documents</t>
+          <t>I certify that the data entered in this eCRF are complete, accurate, and are supported by the source documents</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>I certify that the data entered in this eCRF are complete, accurate, and ae supported by the source documents</t>
+          <t>I certify that the data entered in this eCRF are complete, accurate, and are supported by the source documents</t>
         </is>
       </c>
     </row>
